--- a/01_analyses_states/Puducherry/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Puducherry/results/SoIB_summaries.xlsx
@@ -461,7 +461,7 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
@@ -471,10 +471,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C8">
-        <v>236</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C4">
         <v>0</v>

--- a/01_analyses_states/Puducherry/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Puducherry/results/SoIB_summaries.xlsx
@@ -461,7 +461,7 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
@@ -471,10 +471,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C8">
-        <v>214</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>286</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>553</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>235</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -733,16 +733,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C2">
-        <v>84.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E2">
-        <v>86.09999999999999</v>
+        <v>88.09999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -752,16 +752,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C3">
-        <v>15.5</v>
+        <v>13.6</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E3">
-        <v>13.9</v>
+        <v>11.9</v>
       </c>
     </row>
   </sheetData>
